--- a/Assets/StreamingAssets/Weapons.xlsx
+++ b/Assets/StreamingAssets/Weapons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D21132E-777C-4703-81A7-BD16F4C1ACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65675FA3-55D1-4C76-927D-2C5B3B6ADE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="0" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
+    <workbookView xWindow="0" yWindow="1890" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,156 +60,156 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>probability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhancingPrice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물에빠진 정령의 검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요괴왕의 송곳니 검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 뱀의 독니</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼스터의 단단한 벼락</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악귀 씌인 귀철의 검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양신의 응보검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈염산하의 석자검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddressID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산하동색의 석자검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>82근의 언월도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한정 마술예장의 만화경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아홉머리 뱀을 심판한 천뢰검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필망의 마검 티르핑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>듀랜달</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 자루 무색유리검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마스터 소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트 브링어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4, 6, 12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wooden Sword</t>
+  </si>
+  <si>
+    <t>Ancient Sword</t>
+  </si>
+  <si>
+    <t>Zweihander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Three Great Demon Iron</t>
+  </si>
+  <si>
+    <t>Blue Dragon Crescent Blade</t>
+  </si>
+  <si>
+    <t>Kasaka's Venom Fang</t>
+  </si>
+  <si>
+    <t>Dragon Slayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caladbolg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iron Chain Fang</t>
+  </si>
+  <si>
+    <t>Sword of Admiral Yi Sun-sin 1</t>
+  </si>
+  <si>
+    <t>Sword of Admiral Yi Sun-sin 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excalibur</t>
+  </si>
+  <si>
+    <t>Fragarach</t>
+  </si>
+  <si>
+    <t>Nightbringer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kusanagi-no-Tsurugi</t>
+  </si>
+  <si>
+    <t>Tyrfing</t>
+  </si>
+  <si>
+    <t>Durandal</t>
+  </si>
+  <si>
+    <t>Jeweled Sword</t>
+  </si>
+  <si>
+    <t>Colorless Glass Sword</t>
+  </si>
+  <si>
+    <t>Master Sword</t>
+  </si>
+  <si>
+    <t>NeedItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>probability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnhancingPrice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물에빠진 정령의 검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요괴왕의 송곳니 검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거대한 뱀의 독니</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>얼스터의 단단한 벼락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>악귀 씌인 귀철의 검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>태양신의 응보검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>혈염산하의 석자검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddressID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산하동색의 석자검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>82근의 언월도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한정 마술예장의 만화경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아홉머리 뱀을 심판한 천뢰검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필망의 마검 티르핑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>듀랜달</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 자루 무색유리검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마스터 소드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나이트 브링어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4, 6, 12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wooden Sword</t>
-  </si>
-  <si>
-    <t>Ancient Sword</t>
-  </si>
-  <si>
-    <t>Zweihander</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Three Great Demon Iron</t>
-  </si>
-  <si>
-    <t>Blue Dragon Crescent Blade</t>
-  </si>
-  <si>
-    <t>Kasaka's Venom Fang</t>
-  </si>
-  <si>
-    <t>Dragon Slayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Caladbolg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Iron Chain Fang</t>
-  </si>
-  <si>
-    <t>Sword of Admiral Yi Sun-sin 1</t>
-  </si>
-  <si>
-    <t>Sword of Admiral Yi Sun-sin 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excalibur</t>
-  </si>
-  <si>
-    <t>Fragarach</t>
-  </si>
-  <si>
-    <t>Nightbringer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kusanagi-no-Tsurugi</t>
-  </si>
-  <si>
-    <t>Tyrfing</t>
-  </si>
-  <si>
-    <t>Durandal</t>
-  </si>
-  <si>
-    <t>Jeweled Sword</t>
-  </si>
-  <si>
-    <t>Colorless Glass Sword</t>
-  </si>
-  <si>
-    <t>Master Sword</t>
-  </si>
-  <si>
-    <t>NeedItems</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +587,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -596,16 +596,16 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -625,7 +625,7 @@
         <v>1000</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -645,7 +645,7 @@
         <v>9000</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -665,7 +665,7 @@
         <v>20000</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -673,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>1000000</v>
@@ -685,7 +685,7 @@
         <v>70000</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -693,7 +693,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>2000000</v>
@@ -705,7 +705,7 @@
         <v>120000</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -713,7 +713,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>2800000</v>
@@ -725,7 +725,7 @@
         <v>180000</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -745,7 +745,7 @@
         <v>240000</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -753,7 +753,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>3500000</v>
@@ -765,7 +765,7 @@
         <v>300000</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -773,7 +773,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>4500000</v>
@@ -785,7 +785,7 @@
         <v>380000</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -793,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>7000000</v>
@@ -805,7 +805,7 @@
         <v>650000</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>18000000</v>
@@ -825,10 +825,7 @@
         <v>1500000</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -836,7 +833,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>35000000</v>
@@ -848,7 +845,7 @@
         <v>2800000</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -856,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>90000000</v>
@@ -868,7 +865,7 @@
         <v>7000000</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -876,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>105000000</v>
@@ -888,10 +885,10 @@
         <v>9500000</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -899,7 +896,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>125200000</v>
@@ -911,7 +908,7 @@
         <v>12000000</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -919,7 +916,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>160000000</v>
@@ -931,7 +928,7 @@
         <v>22000000</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17">
         <v>14</v>
@@ -942,7 +939,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>220000000</v>
@@ -954,7 +951,7 @@
         <v>36000000</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -962,7 +959,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>500000000</v>
@@ -974,7 +971,7 @@
         <v>90000000</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -982,7 +979,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>1500000000</v>
@@ -994,7 +991,7 @@
         <v>22000000</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1002,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>4500000000</v>
@@ -1014,7 +1011,7 @@
         <v>60000000</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
